--- a/assets/docs/lop1/Tieng Viet - Lop 1.xlsx
+++ b/assets/docs/lop1/Tieng Viet - Lop 1.xlsx
@@ -547,12 +547,12 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>1 – 3</t>
+          <t>1 – 2</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -582,12 +582,12 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>4 – 6</t>
+          <t>3 – 4</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -612,17 +612,17 @@
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Làm quen với các nét viết cơ bản, các chữ số, dấu thanh và bảng chữ cái</t>
+          <t>Làm quen với các nét cơ bản, các chữ số, bảng chữ cái và dấu thanh</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>7 – 9</t>
+          <t>5 – 10</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -652,12 +652,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>10 – 12</t>
+          <t>11 – 12</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">

--- a/assets/docs/lop1/Tieng Viet - Lop 1.xlsx
+++ b/assets/docs/lop1/Tieng Viet - Lop 1.xlsx
@@ -5067,7 +5067,7 @@
       <c r="D135" s="4" t="inlineStr"/>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Bài 2: Lời chào</t>
+          <t>Bài 2: Lời chào đi trước</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
